--- a/data/raw/GLNPO 2024 Spring/Ontario/D20/Zoops/ON 12 D20 Spring 2024 24GO00I94 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Ontario/D20/Zoops/ON 12 D20 Spring 2024 24GO00I94 Zoop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ccm243\Desktop\GLNPO Counts\2024\Spring\Ontario\D20\Zoops\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Ontario\D20\Zoops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F69B70-F611-40CD-825B-A0C4EA2009A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91A41F8-C302-45A3-B248-F721150E8FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F53B3847-36BD-4C76-A91A-C3EA5957407A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F53B3847-36BD-4C76-A91A-C3EA5957407A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$189</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="730" r:id="rId2"/>
+    <pivotCache cacheId="50" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -399,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -409,7 +409,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4293,7 +4292,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D670F5AC-D227-49E5-84B7-2B38DFD9917F}" name="PivotTable1" cacheId="730" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D670F5AC-D227-49E5-84B7-2B38DFD9917F}" name="PivotTable1" cacheId="50" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T5:X18" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -4727,19 +4726,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67B96C40-8AD5-4A07-BD14-EA58BABDA045}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:X189"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.28515625" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" customWidth="1"/>
-    <col min="24" max="24" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.33203125" customWidth="1"/>
+    <col min="23" max="23" width="6.6640625" customWidth="1"/>
+    <col min="24" max="24" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -4848,7 +4848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5013,7 +5013,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -5081,7 +5081,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -5136,16 +5136,14 @@
       <c r="T7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="U7" s="7">
+      <c r="U7">
         <v>26</v>
       </c>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7">
+      <c r="X7">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -5200,16 +5198,14 @@
       <c r="T8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="U8" s="7">
+      <c r="U8">
         <v>61</v>
       </c>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7">
+      <c r="X8">
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -5264,18 +5260,17 @@
       <c r="T9" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="U9" s="7">
+      <c r="U9">
         <v>6</v>
       </c>
-      <c r="V9" s="7">
+      <c r="V9">
         <v>15</v>
       </c>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -5330,18 +5325,17 @@
       <c r="T10" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="U10" s="7">
+      <c r="U10">
         <v>3</v>
       </c>
-      <c r="V10" s="7">
+      <c r="V10">
         <v>2</v>
       </c>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7">
+      <c r="X10">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -5396,16 +5390,14 @@
       <c r="T11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="U11" s="7">
+      <c r="U11">
         <v>68</v>
       </c>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7">
+      <c r="X11">
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -5460,16 +5452,14 @@
       <c r="T12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="U12" s="7">
+      <c r="U12">
         <v>72</v>
       </c>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7">
+      <c r="X12">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -5524,16 +5514,14 @@
       <c r="T13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="U13" s="7">
+      <c r="U13">
         <v>32</v>
       </c>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7">
+      <c r="X13">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -5588,18 +5576,17 @@
       <c r="T14" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="U14" s="7">
+      <c r="U14">
         <v>2</v>
       </c>
-      <c r="V14" s="7">
+      <c r="V14">
         <v>3</v>
       </c>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7">
+      <c r="X14">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -5654,18 +5641,17 @@
       <c r="T15" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="U15" s="7">
+      <c r="U15">
         <v>14</v>
       </c>
-      <c r="V15" s="7">
-        <v>16</v>
-      </c>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7">
+      <c r="V15">
+        <v>16</v>
+      </c>
+      <c r="X15">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -5720,20 +5706,20 @@
       <c r="T16" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="U16" s="7">
+      <c r="U16">
         <v>0</v>
       </c>
-      <c r="V16" s="7">
+      <c r="V16">
         <v>0</v>
       </c>
-      <c r="W16" s="7">
-        <v>1</v>
-      </c>
-      <c r="X16" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="W16">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -5788,18 +5774,17 @@
       <c r="T17" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="U17" s="7">
-        <v>16</v>
-      </c>
-      <c r="V17" s="7">
-        <v>16</v>
-      </c>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7">
+      <c r="U17">
+        <v>16</v>
+      </c>
+      <c r="V17">
+        <v>16</v>
+      </c>
+      <c r="X17">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -5854,20 +5839,20 @@
       <c r="T18" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="U18" s="7">
+      <c r="U18">
         <v>300</v>
       </c>
-      <c r="V18" s="7">
+      <c r="V18">
         <v>52</v>
       </c>
-      <c r="W18" s="7">
-        <v>1</v>
-      </c>
-      <c r="X18" s="7">
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18">
         <v>353</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -5920,7 +5905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -5973,7 +5958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -6026,7 +6011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -6078,17 +6063,17 @@
       <c r="Q22">
         <v>1</v>
       </c>
-      <c r="T22" s="8" t="s">
+      <c r="T22" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="U22" s="9" t="s">
+      <c r="U22" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="V22" s="10">
+      <c r="V22" s="9">
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -6140,15 +6125,15 @@
       <c r="Q23">
         <v>1</v>
       </c>
-      <c r="T23" s="11"/>
-      <c r="U23" s="9" t="s">
+      <c r="T23" s="10"/>
+      <c r="U23" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="V23" s="10">
+      <c r="V23" s="9">
         <v>0.996</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -6200,17 +6185,17 @@
       <c r="Q24">
         <v>1</v>
       </c>
-      <c r="T24" s="8" t="s">
+      <c r="T24" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="U24" s="9" t="s">
+      <c r="U24" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="V24" s="10">
+      <c r="V24" s="9">
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -6262,15 +6247,15 @@
       <c r="Q25">
         <v>1</v>
       </c>
-      <c r="T25" s="11"/>
-      <c r="U25" s="9" t="s">
+      <c r="T25" s="10"/>
+      <c r="U25" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="V25" s="10">
+      <c r="V25" s="9">
         <v>0.999</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -6322,15 +6307,15 @@
       <c r="Q26">
         <v>1</v>
       </c>
-      <c r="T26" s="12" t="s">
+      <c r="T26" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="U26" s="13" t="s">
+      <c r="U26" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="V26" s="14"/>
-    </row>
-    <row r="27" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="V26" s="13"/>
+    </row>
+    <row r="27" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -6385,15 +6370,15 @@
       <c r="R27" t="s">
         <v>48</v>
       </c>
-      <c r="T27" s="12" t="s">
+      <c r="T27" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="U27" s="13" t="s">
+      <c r="U27" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="V27" s="14"/>
-    </row>
-    <row r="28" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="V27" s="13"/>
+    </row>
+    <row r="28" spans="1:24" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -6445,13 +6430,13 @@
       <c r="Q28">
         <v>1</v>
       </c>
-      <c r="T28" s="9" t="s">
+      <c r="T28" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="U28" s="13"/>
-      <c r="V28" s="14"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="U28" s="12"/>
+      <c r="V28" s="13"/>
+    </row>
+    <row r="29" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -6504,7 +6489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -6557,7 +6542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -6610,7 +6595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -6663,7 +6648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -6716,7 +6701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -6769,7 +6754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -6822,7 +6807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -6875,7 +6860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -6928,7 +6913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -6981,7 +6966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -7034,7 +7019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -7087,7 +7072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -7140,7 +7125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -7193,7 +7178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -7246,7 +7231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -7299,7 +7284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -7352,7 +7337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -7405,7 +7390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -7458,7 +7443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -7511,7 +7496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -7564,7 +7549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -7617,7 +7602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -7670,7 +7655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -7723,7 +7708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -7776,7 +7761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -7829,7 +7814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -7882,7 +7867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -7935,7 +7920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -7988,7 +7973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -8041,7 +8026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -8094,7 +8079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -8147,7 +8132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -8200,7 +8185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -8253,7 +8238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -8306,7 +8291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -8359,7 +8344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -8412,7 +8397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -8465,7 +8450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -8518,7 +8503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -8571,7 +8556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -8624,7 +8609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -8677,7 +8662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -8730,7 +8715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -8783,7 +8768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -8836,7 +8821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -8889,7 +8874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -8942,7 +8927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -8995,7 +8980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -9048,7 +9033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -9101,7 +9086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -9157,7 +9142,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -9210,7 +9195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -9263,7 +9248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -9316,7 +9301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -9369,7 +9354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -9422,7 +9407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -9475,7 +9460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -9528,7 +9513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -9581,7 +9566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -9634,7 +9619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -9687,7 +9672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -9740,7 +9725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -9793,7 +9778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -9846,7 +9831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -9899,7 +9884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -9952,7 +9937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -10005,7 +9990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -10058,7 +10043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -10111,7 +10096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -10164,7 +10149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -10217,7 +10202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -10270,7 +10255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -10323,7 +10308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -10376,7 +10361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -10429,7 +10414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -10482,7 +10467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -10538,7 +10523,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -10591,7 +10576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -10644,7 +10629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -10697,7 +10682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -10750,7 +10735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -10803,7 +10788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -10856,7 +10841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -10909,7 +10894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -10962,7 +10947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -11015,7 +11000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -11068,7 +11053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -11121,7 +11106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -11174,7 +11159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -11227,7 +11212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -11280,7 +11265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -11333,7 +11318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -11386,7 +11371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -11439,7 +11424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -11492,7 +11477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -11545,7 +11530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -11598,7 +11583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -11651,7 +11636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -11704,7 +11689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -11757,7 +11742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -11810,7 +11795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -11857,13 +11842,13 @@
         <v>1.3</v>
       </c>
       <c r="P130" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q130">
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -11919,7 +11904,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -11972,7 +11957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -12025,7 +12010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -12078,7 +12063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -12131,7 +12116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -12184,7 +12169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -12237,7 +12222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -12290,7 +12275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -12343,7 +12328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -12396,7 +12381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -12449,7 +12434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -12502,7 +12487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -12555,7 +12540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -12608,7 +12593,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -12661,7 +12646,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -12714,7 +12699,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -12767,7 +12752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -12820,7 +12805,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -12873,7 +12858,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -12926,7 +12911,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -12979,7 +12964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -13032,7 +13017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -13085,7 +13070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -13138,7 +13123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -13191,7 +13176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -13244,7 +13229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -13297,7 +13282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -13350,7 +13335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -13403,7 +13388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -13456,7 +13441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -13509,7 +13494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -13562,7 +13547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -13615,7 +13600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -13668,7 +13653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -13721,7 +13706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -13774,7 +13759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -13827,7 +13812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -13880,7 +13865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -13933,7 +13918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -13986,7 +13971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -14039,7 +14024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -14092,7 +14077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -14145,7 +14130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -14198,7 +14183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -14251,7 +14236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -14304,7 +14289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -14357,7 +14342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -14410,7 +14395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -14463,7 +14448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -14516,7 +14501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -14569,7 +14554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -14622,7 +14607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -14675,7 +14660,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -14728,7 +14713,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -14781,7 +14766,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -14834,7 +14819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -14887,7 +14872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>18</v>
       </c>
@@ -14940,7 +14925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>18</v>
       </c>
@@ -14994,6 +14979,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R189" xr:uid="{67B96C40-8AD5-4A07-BD14-EA58BABDA045}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Skistodiaptomus oregonensis"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>